--- a/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -523,7 +523,7 @@
         <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -1453,7 +1453,7 @@
         <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
@@ -1515,7 +1515,7 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>53</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" t="n">
         <v>7</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>17</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>20</v>
@@ -7405,7 +7405,7 @@
         <v>33</v>
       </c>
       <c r="F113" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
         <v>33</v>
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F143" t="n">
         <v>38</v>
@@ -9277,10 +9277,10 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -11435,7 +11435,7 @@
         <v>38</v>
       </c>
       <c r="F178" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K178" t="n">
         <v>38</v>

--- a/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
@@ -783,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>53</v>
@@ -2693,7 +2693,7 @@
         <v>57</v>
       </c>
       <c r="F37" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>57</v>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3759,10 +3759,10 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F73" t="n">
         <v>22</v>
@@ -4937,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
         <v>11</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>23</v>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G78" t="n">
         <v>10</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K78" t="n">
         <v>24</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>3</v>
@@ -5433,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F82" t="n">
         <v>101</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F83" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G83" t="n">
         <v>20</v>
@@ -5557,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L83" t="n">
         <v>2</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>185</v>
@@ -5752,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>2</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
@@ -6239,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -6475,7 +6475,7 @@
         <v>5</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
@@ -6487,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
         <v>5</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
         <v>3</v>
@@ -6549,10 +6549,10 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
         <v>3</v>
@@ -6611,10 +6611,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F101" t="n">
         <v>4</v>
@@ -6673,10 +6673,10 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         <v>110</v>
       </c>
       <c r="F105" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>110</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F106" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L106" t="n">
         <v>1</v>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -7045,16 +7045,16 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7107,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
         <v>1</v>
-      </c>
-      <c r="K112" t="n">
-        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F113" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
         <v>15</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7792,10 +7792,10 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
         <v>26</v>
@@ -8037,10 +8037,10 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K123" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>91</v>
       </c>
       <c r="F126" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
         <v>91</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F127" t="n">
         <v>26</v>
@@ -8285,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
         <v>3</v>
@@ -8719,10 +8719,10 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F142" t="n">
         <v>55</v>
@@ -9215,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9265,7 +9265,7 @@
         <v>38</v>
       </c>
       <c r="F143" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
         <v>38</v>
@@ -10257,7 +10257,7 @@
         <v>10</v>
       </c>
       <c r="F159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
         <v>14</v>
@@ -10517,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10644,10 +10644,10 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -11063,7 +11063,7 @@
         <v>35</v>
       </c>
       <c r="F172" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
         <v>35</v>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F178" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11447,10 +11447,10 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
         <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -709,7 +709,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>19</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
         <v>51</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
         <v>16</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F86" t="n">
         <v>183</v>
@@ -5743,10 +5743,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -9141,7 +9141,7 @@
         <v>4</v>
       </c>
       <c r="F141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>4</v>
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F143" t="n">
         <v>36</v>
@@ -9277,10 +9277,10 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -10917,12 +10917,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA80128</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0H1H3K6B2</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -10979,12 +10979,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA80141</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -11041,12 +11041,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA80142</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0H3LHF2WW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11056,14 +11056,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AM-C5 White</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11078,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -11103,12 +11103,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA80143</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0H1MTP2ZP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11118,14 +11118,14 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -11140,7 +11140,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -11165,12 +11165,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBI76864</t>
+          <t>FBA80128</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0H1H3K6B2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -11227,12 +11227,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11242,14 +11242,14 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -11264,7 +11264,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -11289,12 +11289,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBA80142</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0H3LHF2WW</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C5 White</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F176" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -11351,12 +11351,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBK79708</t>
+          <t>FBA80143</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0FJS7JZ4V</t>
+          <t>B0H1MTP2ZP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11366,14 +11366,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -11413,12 +11413,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBM79783</t>
+          <t>FBI76864</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11428,14 +11428,14 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11447,10 +11447,10 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -11475,12 +11475,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11490,14 +11490,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -11512,17 +11512,17 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>CAMBIUMRETAIL</t>
+          <t>AUDIOARRAY</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11537,12 +11537,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11552,14 +11552,14 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>CAMBIUMRETAIL</t>
+          <t>AUDIOARRAY</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11599,12 +11599,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBK79708</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0FJS7JZ4V</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -11636,17 +11636,17 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>CAMBIUMRETAIL</t>
+          <t>AUDIOARRAY</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11661,12 +11661,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBM79783</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11676,14 +11676,14 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -11695,10 +11695,10 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>AUDIOARRAY</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11723,12 +11723,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11738,14 +11738,14 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -11760,17 +11760,17 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>CAMBIUMRETAIL</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -11785,12 +11785,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11800,14 +11800,14 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -11822,7 +11822,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>CAMBIUMRETAIL</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -11847,12 +11847,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11862,14 +11862,14 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>CAMBIUMRETAIL</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -11909,12 +11909,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11924,14 +11924,14 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -11946,7 +11946,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -11971,12 +11971,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11986,14 +11986,14 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -12008,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -12033,12 +12033,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12048,14 +12048,14 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12070,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -12095,12 +12095,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12110,14 +12110,14 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -12157,12 +12157,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -12219,12 +12219,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -12281,12 +12281,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -12343,12 +12343,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -12380,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -12405,12 +12405,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12420,14 +12420,14 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -12467,12 +12467,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -12529,12 +12529,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12544,14 +12544,14 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -12591,62 +12591,310 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>FBA79445</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>B0DFMLS8JG</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>AM-W32</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>33</v>
+      </c>
+      <c r="F197" t="n">
+        <v>33</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>33</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FBA79448</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>B0DFMKY4TT</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>AM-W35</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FBA79722</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>B0F2HYY7JF</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>AM-W21</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FBA79816</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>FBA76864</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>B0BPLZ5CGV</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
         <is>
           <t>AI-04 Red</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="inlineStr">
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>WHITEMULBERRY</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="P197" t="n">
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
         <v>30</v>
       </c>
     </row>
